--- a/Excel/12_SupplementaryCO2_WIP_v02.xlsx
+++ b/Excel/12_SupplementaryCO2_WIP_v02.xlsx
@@ -787,108 +787,106 @@
   </numFmts>
   <fonts count="52" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -899,238 +897,232 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="16"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="18"/>
+      <color theme="3" tint="9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1987,11 +1979,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.249977111117893"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2018,11 +2009,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.14999847407452621"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -2068,11 +2058,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2092,11 +2081,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2116,11 +2104,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2140,11 +2127,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2164,11 +2150,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2188,11 +2173,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2212,11 +2196,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2236,11 +2219,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2260,11 +2242,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2284,11 +2265,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2308,11 +2288,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2332,11 +2311,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2356,11 +2334,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2380,11 +2357,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2404,11 +2380,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2428,11 +2403,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2452,11 +2426,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2476,11 +2449,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2500,11 +2472,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2524,11 +2495,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2548,11 +2518,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2572,11 +2541,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2596,11 +2564,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2620,11 +2587,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2644,11 +2610,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2668,11 +2633,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2692,11 +2656,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2716,11 +2679,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2740,11 +2702,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2764,11 +2725,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2788,11 +2748,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2812,11 +2771,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2836,11 +2794,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2860,11 +2817,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2884,11 +2840,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2908,11 +2863,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2932,11 +2886,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3242,17 +3195,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{656D3250-5DC9-4557-91D1-8936CA4BCBE6}" type="TxLink">
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>12.1.1-2 Supplementary CO2</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1400" b="0">
+          <a:endParaRPr lang="en-AU" sz="1200" b="0">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3324,17 +3277,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{4FABD2FB-7C1B-45AA-B92C-732AA970345B}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Emissions from the use of supplementary CO2</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000" b="1">
+          <a:endParaRPr lang="en-AU" sz="900" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3407,14 +3360,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -3422,13 +3375,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐶𝐻</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>4</m:t>
@@ -3436,7 +3389,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -3446,14 +3399,14 @@
                         <m:chr m:val="∑"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑗</m:t>
@@ -3466,14 +3419,14 @@
                             <m:chr m:val="∑"/>
                             <m:supHide m:val="on"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:naryPr>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑘</m:t>
@@ -3486,14 +3439,14 @@
                                 <m:chr m:val="∑"/>
                                 <m:supHide m:val="on"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:naryPr>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑚</m:t>
@@ -3506,14 +3459,14 @@
                                     <m:chr m:val="∑"/>
                                     <m:supHide m:val="on"/>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:naryPr>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑇</m:t>
@@ -3524,7 +3477,7 @@
                                     <m:d>
                                       <m:dPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
@@ -3533,14 +3486,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝐷</m:t>
@@ -3548,7 +3501,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -3556,7 +3509,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -3564,14 +3517,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑀</m:t>
@@ -3579,7 +3532,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘𝑚𝑇</m:t>
@@ -3587,7 +3540,7 @@
                                           </m:sub>
                                         </m:sSub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>×</m:t>
@@ -3595,14 +3548,14 @@
                                         <m:sSub>
                                           <m:sSubPr>
                                             <m:ctrlPr>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                             </m:ctrlPr>
                                           </m:sSubPr>
                                           <m:e>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑁</m:t>
@@ -3610,7 +3563,7 @@
                                           </m:e>
                                           <m:sub>
                                             <m:r>
-                                              <a:rPr lang="en-AU" sz="1100" i="1">
+                                              <a:rPr lang="en-AU" sz="1000" i="1">
                                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                               </a:rPr>
                                               <m:t>𝑗𝑘</m:t>
@@ -3628,7 +3581,7 @@
                       </m:e>
                     </m:nary>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -3636,14 +3589,14 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>10</m:t>
@@ -3651,7 +3604,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−3</m:t>
@@ -3661,7 +3614,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3709,12 +3662,12 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝐶𝐻4=∑8_𝑗▒∑8_𝑘▒∑8_𝑚▒∑8_𝑇▒(𝐷_𝑗𝑘×𝑀_𝑗𝑘𝑚𝑇×𝑁_𝑗𝑘 ) ×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3794,7 +3747,7 @@
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMath>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:solidFill>
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
@@ -3806,7 +3759,7 @@
                       <m:t>𝐸</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:solidFill>
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
@@ -3818,7 +3771,7 @@
                       <m:t>=</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:solidFill>
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
@@ -3830,7 +3783,7 @@
                       <m:t>𝑄</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:solidFill>
                           <a:schemeClr val="tx1"/>
                         </a:solidFill>
@@ -3844,7 +3797,7 @@
                     <m:sSup>
                       <m:sSupPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -3857,7 +3810,7 @@
                       </m:sSupPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -3871,7 +3824,7 @@
                       </m:e>
                       <m:sup>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:solidFill>
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
@@ -3887,7 +3840,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3952,7 +3905,7 @@
                 <a:defRPr/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -3963,7 +3916,7 @@
                 </a:rPr>
                 <a:t>𝐸=𝑄×10^(−3)</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4617,12 +4570,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -4833,31 +4786,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="67" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="65" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -4874,7 +4827,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:W45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -4904,7 +4857,7 @@
       <c r="O1" s="52"/>
       <c r="P1" s="52"/>
     </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="52"/>
       <c r="D2" s="52"/>
       <c r="E2" s="52"/>
@@ -4921,7 +4874,7 @@
       <c r="P2" s="52"/>
       <c r="Q2" s="53"/>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -4941,13 +4894,13 @@
       <c r="O3" s="54"/>
       <c r="P3" s="54"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -4967,7 +4920,7 @@
       <c r="N5" s="33"/>
       <c r="O5" s="30"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="55" t="s">
         <v>83</v>
       </c>
@@ -4983,78 +4936,78 @@
       <c r="N6" s="32"/>
       <c r="O6" s="31"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="12:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:23" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="W45" t="s">
         <v>81</v>
       </c>
@@ -5072,7 +5025,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:H87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -5090,10 +5043,10 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -5105,7 +5058,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -5119,7 +5072,7 @@
       <c r="G4" s="17"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="41" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -5131,7 +5084,7 @@
       <c r="G5" s="20"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="16"/>
       <c r="D6" s="15" t="s">
         <v>79</v>
@@ -5141,7 +5094,7 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -5149,7 +5102,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -5168,7 +5121,7 @@
       </c>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
@@ -5190,7 +5143,7 @@
       </c>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="16"/>
       <c r="D10" s="22" t="s">
         <v>54</v>
@@ -5208,7 +5161,7 @@
       </c>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="16"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -5216,7 +5169,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -5227,7 +5180,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
@@ -5239,7 +5192,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="16"/>
       <c r="D14" s="1"/>
       <c r="E14" s="38"/>
@@ -5247,7 +5200,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="16"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -5255,7 +5208,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>1</v>
       </c>
@@ -5266,7 +5219,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -5278,7 +5231,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="16"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -5286,7 +5239,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="16"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -5294,7 +5247,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="16"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -5302,7 +5255,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="16"/>
       <c r="D21" s="1"/>
       <c r="E21" s="38"/>
@@ -5310,7 +5263,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="16"/>
       <c r="D22" s="1"/>
       <c r="E22" s="38"/>
@@ -5318,7 +5271,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="16"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -5326,7 +5279,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="16"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -5334,7 +5287,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="16"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -5342,7 +5295,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="16"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -5350,7 +5303,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="16"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -5358,7 +5311,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="16"/>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="16"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -5366,7 +5319,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="16"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -5374,7 +5327,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="16"/>
     </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="16"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -5382,7 +5335,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="16"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -5390,7 +5343,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="16"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -5398,7 +5351,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="16"/>
     </row>
-    <row r="33" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="16"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -5406,7 +5359,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="16"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -5414,7 +5367,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="16"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -5422,7 +5375,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="16"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -5430,7 +5383,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="16"/>
     </row>
-    <row r="37" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="16"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -5438,7 +5391,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="16"/>
     </row>
-    <row r="38" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="16"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -5446,7 +5399,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="16"/>
     </row>
-    <row r="39" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="16"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -5454,7 +5407,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="16"/>
     </row>
-    <row r="40" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -5462,7 +5415,7 @@
       <c r="G40" s="1"/>
       <c r="H40" s="16"/>
     </row>
-    <row r="41" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="16"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -5470,7 +5423,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="16"/>
     </row>
-    <row r="42" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="16"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -5478,7 +5431,7 @@
       <c r="G42" s="1"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="16"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -5486,7 +5439,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="16"/>
     </row>
-    <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="16"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -5494,7 +5447,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="16"/>
     </row>
-    <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="16"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -5502,7 +5455,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="16"/>
     </row>
-    <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="16"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -5510,7 +5463,7 @@
       <c r="G46" s="1"/>
       <c r="H46" s="16"/>
     </row>
-    <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="16"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5518,7 +5471,7 @@
       <c r="G47" s="1"/>
       <c r="H47" s="16"/>
     </row>
-    <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="16"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5526,7 +5479,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="16"/>
     </row>
-    <row r="49" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="16"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -5534,7 +5487,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="16"/>
     </row>
-    <row r="50" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="16"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -5542,7 +5495,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="16"/>
     </row>
-    <row r="51" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="16"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -5550,7 +5503,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="16"/>
     </row>
-    <row r="52" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="16"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -5558,7 +5511,7 @@
       <c r="G52" s="1"/>
       <c r="H52" s="16"/>
     </row>
-    <row r="53" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="16"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5566,7 +5519,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="16"/>
     </row>
-    <row r="54" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="16"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -5574,7 +5527,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="16"/>
     </row>
-    <row r="55" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="16"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -5582,7 +5535,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="16"/>
     </row>
-    <row r="56" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="16"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -5590,7 +5543,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="16"/>
     </row>
-    <row r="57" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="16"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -5598,7 +5551,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="16"/>
     </row>
-    <row r="58" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="16"/>
       <c r="D58" s="1"/>
       <c r="E58" s="23"/>
@@ -5606,7 +5559,7 @@
       <c r="G58" s="16"/>
       <c r="H58" s="16"/>
     </row>
-    <row r="59" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="16"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -5614,7 +5567,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="16"/>
     </row>
-    <row r="60" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="16"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -5622,7 +5575,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="16"/>
     </row>
-    <row r="61" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="16"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -5630,7 +5583,7 @@
       <c r="G61" s="1"/>
       <c r="H61" s="16"/>
     </row>
-    <row r="62" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="16"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -5638,7 +5591,7 @@
       <c r="G62" s="1"/>
       <c r="H62" s="16"/>
     </row>
-    <row r="63" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="16"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -5646,7 +5599,7 @@
       <c r="G63" s="1"/>
       <c r="H63" s="16"/>
     </row>
-    <row r="64" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="16"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -5654,7 +5607,7 @@
       <c r="G64" s="1"/>
       <c r="H64" s="16"/>
     </row>
-    <row r="65" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="16"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -5662,7 +5615,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="16"/>
     </row>
-    <row r="66" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="16"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -5670,7 +5623,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="16"/>
     </row>
-    <row r="67" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="16"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -5678,7 +5631,7 @@
       <c r="G67" s="1"/>
       <c r="H67" s="16"/>
     </row>
-    <row r="68" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="16"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -5686,7 +5639,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="16"/>
     </row>
-    <row r="69" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="16"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -5694,7 +5647,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="16"/>
     </row>
-    <row r="70" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="16"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -5702,7 +5655,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="16"/>
     </row>
-    <row r="71" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="16"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -5710,7 +5663,7 @@
       <c r="G71" s="1"/>
       <c r="H71" s="16"/>
     </row>
-    <row r="72" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="16"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -5718,7 +5671,7 @@
       <c r="G72" s="1"/>
       <c r="H72" s="16"/>
     </row>
-    <row r="73" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="16"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -5726,7 +5679,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="16"/>
     </row>
-    <row r="74" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="16"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -5734,7 +5687,7 @@
       <c r="G74" s="1"/>
       <c r="H74" s="16"/>
     </row>
-    <row r="75" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="16"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -5742,7 +5695,7 @@
       <c r="G75" s="1"/>
       <c r="H75" s="16"/>
     </row>
-    <row r="76" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="16"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -5750,7 +5703,7 @@
       <c r="G76" s="1"/>
       <c r="H76" s="16"/>
     </row>
-    <row r="77" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="16"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -5758,7 +5711,7 @@
       <c r="G77" s="1"/>
       <c r="H77" s="16"/>
     </row>
-    <row r="78" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="16"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -5766,7 +5719,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="16"/>
     </row>
-    <row r="79" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="16"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -5774,7 +5727,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="16"/>
     </row>
-    <row r="80" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="16"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -5782,7 +5735,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="16"/>
     </row>
-    <row r="81" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="16"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -5790,7 +5743,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="16"/>
     </row>
-    <row r="82" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="16"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -5798,7 +5751,7 @@
       <c r="G82" s="1"/>
       <c r="H82" s="16"/>
     </row>
-    <row r="83" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="16"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -5806,7 +5759,7 @@
       <c r="G83" s="1"/>
       <c r="H83" s="16"/>
     </row>
-    <row r="84" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="16"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -5814,7 +5767,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="16"/>
     </row>
-    <row r="85" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="16"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5822,7 +5775,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="16"/>
     </row>
-    <row r="86" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
@@ -5830,7 +5783,7 @@
       <c r="G86" s="16"/>
       <c r="H86" s="16"/>
     </row>
-    <row r="87" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
       <c r="E87" s="16"/>
@@ -5849,7 +5802,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G351"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -5869,10 +5822,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -5883,13 +5836,13 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -5900,19 +5853,19 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
     </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="59" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="60"/>
       <c r="F7" s="58"/>
     </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -5920,7 +5873,7 @@
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="40" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
@@ -5933,7 +5886,7 @@
       </c>
       <c r="F9" s="16"/>
     </row>
-    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="61" t="s">
         <v>90</v>
       </c>
@@ -5941,7 +5894,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="61" t="s">
         <v>91</v>
       </c>
@@ -5949,59 +5902,59 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="45"/>
       <c r="G38" s="45"/>
     </row>
-    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="45"/>
       <c r="G39" s="45"/>
     </row>
-    <row r="40" spans="1:7" s="46" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="46" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -6009,7 +5962,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" s="46" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="46" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -6017,131 +5970,131 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="4:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D351" s="35"/>
     </row>
   </sheetData>
@@ -6235,7 +6188,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:P342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -6253,10 +6206,10 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6278,13 +6231,13 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6295,14 +6248,14 @@
       </c>
       <c r="O5" s="42"/>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">SupplementaryCO2_Equations.VEERG_12_1_1_1__1_EmissionsFromSupplementaryCO2_Source()</f>
         <v>VEERG 2026: 12.1.1.1, Equation (1)</v>
       </c>
       <c r="O6" s="42"/>
     </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
@@ -6312,13 +6265,13 @@
       </c>
       <c r="O7" s="42"/>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
       <c r="O8" s="42"/>
     </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - CO2 Use'!A1", "CO2 Use")</f>
         <v>CO2 Use</v>
@@ -6326,7 +6279,7 @@
       <c r="G9" s="4"/>
       <c r="O9" s="42"/>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="26" t="s">
         <v>12</v>
       </c>
@@ -6336,7 +6289,7 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="26" t="s">
         <v>4</v>
       </c>
@@ -6346,12 +6299,12 @@
       </c>
       <c r="O11" s="42"/>
     </row>
-    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="str">
         <f>HYPERLINK("#'12.1.1-2 Supplementary CO2'!A1", "12.1.1-2 Supplementary CO2")</f>
         <v>12.1.1-2 Supplementary CO2</v>
@@ -6376,10 +6329,10 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14" s="42"/>
     </row>
-    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="62" t="s">
         <v>93</v>
       </c>
@@ -6393,13 +6346,13 @@
       </c>
       <c r="O15" s="42"/>
     </row>
-    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="65" t="s">
         <v>1</v>
       </c>
       <c r="O16" s="42"/>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -6409,281 +6362,281 @@
       <c r="N17" s="42"/>
       <c r="O17" s="42"/>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L18" s="42"/>
       <c r="M18" s="42"/>
       <c r="N18" s="42"/>
       <c r="O18" s="42"/>
     </row>
-    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L19" s="42"/>
       <c r="M19" s="42"/>
       <c r="N19" s="42"/>
       <c r="O19" s="42"/>
     </row>
-    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L20" s="42"/>
       <c r="M20" s="42"/>
       <c r="N20" s="42"/>
       <c r="O20" s="42"/>
     </row>
-    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O21" s="42"/>
     </row>
-    <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="16"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="16"/>
     </row>
   </sheetData>
@@ -6702,7 +6655,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="6" customWidth="1"/>
@@ -6735,10 +6688,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6765,11 +6718,11 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="2"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -6777,7 +6730,7 @@
       </c>
       <c r="BM5" s="2"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>1</v>
       </c>
@@ -6791,7 +6744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="66" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -6809,7 +6762,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -6827,7 +6780,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="25" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -6842,7 +6795,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="25" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -6857,7 +6810,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="25" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -6873,7 +6826,7 @@
       </c>
       <c r="BM11" s="2"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="25" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -6889,7 +6842,7 @@
       </c>
       <c r="BM12" s="2"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="25" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -6904,7 +6857,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="25" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -6919,129 +6872,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="5" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="4" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="25" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="25" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="25" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="25" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="25" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="25" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="25" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="25" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="25" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="25" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="5" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="4" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="25" t="s">
         <v>10</v>
@@ -7050,7 +7003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="25" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7061,7 +7014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="25" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7072,7 +7025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="25" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7083,7 +7036,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="25" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7094,7 +7047,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="25" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7105,7 +7058,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="25" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7116,7 +7069,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="25" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -7127,24 +7080,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="5" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="4" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="25" t="s">
         <v>10</v>
@@ -7162,7 +7115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="25" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7185,7 +7138,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="25" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7208,7 +7161,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="25" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7231,7 +7184,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="25" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7254,7 +7207,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="25" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7277,7 +7230,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="25" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7300,7 +7253,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="25" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -7323,49 +7276,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="5" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="4" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="28" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="28" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="28" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="25" t="s">
         <v>3</v>
@@ -7374,7 +7327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="25" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7385,7 +7338,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="25" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7396,7 +7349,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="25" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7407,7 +7360,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="25" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7418,7 +7371,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="25" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7429,7 +7382,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="25" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7440,7 +7393,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="25" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7451,7 +7404,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="25" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7462,7 +7415,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="25" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7473,7 +7426,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="25" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7484,7 +7437,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="25" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7495,7 +7448,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="25" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7506,7 +7459,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="25" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7517,7 +7470,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="25" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -7528,64 +7481,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="5" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="4" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="28" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="28" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="28" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="28" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="28" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="25" t="s">
         <v>3</v>
@@ -7637,7 +7590,7 @@
       </c>
       <c r="T89" s="25"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="25" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -7705,7 +7658,7 @@
       </c>
       <c r="T90" s="25"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="25" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -7773,7 +7726,7 @@
       </c>
       <c r="T91" s="25"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="25" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -7841,7 +7794,7 @@
       </c>
       <c r="T92" s="25"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="25" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -7909,7 +7862,7 @@
       </c>
       <c r="T93" s="25"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="25" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -7977,7 +7930,7 @@
       </c>
       <c r="T94" s="25"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="25" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -8045,7 +7998,7 @@
       </c>
       <c r="T95" s="25"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="25" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -8113,7 +8066,7 @@
       </c>
       <c r="T96" s="25"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="25" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -8181,66 +8134,66 @@
       </c>
       <c r="T97" s="25"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="27" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="27" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="27" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="27" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="27"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="5" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="4" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="28" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="25" t="s">
         <v>35</v>
@@ -8255,7 +8208,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="25" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -8274,7 +8227,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="25" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -8293,7 +8246,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="25" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -8312,13 +8265,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="5" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -8326,7 +8279,7 @@
       </c>
       <c r="BN115" s="6"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="4" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -8334,7 +8287,7 @@
       </c>
       <c r="BN116" s="6"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="28" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -8342,11 +8295,11 @@
       </c>
       <c r="BN117" s="6"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="6"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="25" t="s">
         <v>38</v>
@@ -8362,7 +8315,7 @@
       </c>
       <c r="BN119" s="6"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="25" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -8382,7 +8335,7 @@
       </c>
       <c r="BN120" s="6"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="25" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -8402,31 +8355,31 @@
       </c>
       <c r="BN121" s="6"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="6"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="5" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="4" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="25" t="s">
         <v>40</v>
@@ -8435,7 +8388,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="25" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -8446,7 +8399,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="25" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -8457,13 +8410,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="5" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -8471,7 +8424,7 @@
       </c>
       <c r="E132" s="16"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="4" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -8479,7 +8432,7 @@
       </c>
       <c r="E133" s="16"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>46</v>
@@ -8488,7 +8441,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -8499,7 +8452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -8510,10 +8463,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="6"/>
       <c r="BO138" s="6"/>
@@ -8528,7 +8481,7 @@
       <c r="BX138" s="6"/>
       <c r="BY138" s="6"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="5" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -8547,7 +8500,7 @@
       <c r="BX139" s="6"/>
       <c r="BY139" s="6"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="4" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -8566,7 +8519,7 @@
       <c r="BX140" s="6"/>
       <c r="BY140" s="6"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="28" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -8574,7 +8527,7 @@
       </c>
       <c r="BN141" s="6"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="25" t="s">
         <v>57</v>
@@ -8584,7 +8537,7 @@
       </c>
       <c r="BN142" s="6"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="25" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -8596,7 +8549,7 @@
       </c>
       <c r="BN143" s="6"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -8608,7 +8561,7 @@
       </c>
       <c r="BN144" s="6"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -8620,7 +8573,7 @@
       </c>
       <c r="BN145" s="6"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -8632,7 +8585,7 @@
       </c>
       <c r="BN146" s="6"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -8644,15 +8597,15 @@
       </c>
       <c r="BN147" s="6"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="6"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="6"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="5" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -8660,7 +8613,7 @@
       </c>
       <c r="BN150" s="6"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="4" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -8668,11 +8621,11 @@
       </c>
       <c r="BN151" s="6"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="6"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="25" t="s">
         <v>42</v>
@@ -8692,7 +8645,7 @@
       <c r="BL153" s="2"/>
       <c r="BM153" s="2"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="25" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -8714,7 +8667,7 @@
       <c r="BL154" s="2"/>
       <c r="BM154" s="2"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="25" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -8736,7 +8689,7 @@
       <c r="BL155" s="2"/>
       <c r="BM155" s="2"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="25" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -8747,7 +8700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="25" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -8758,7 +8711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="25" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -8769,34 +8722,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="5" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="16"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="4" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="16"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="16"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="16" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -8805,17 +8758,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="6"/>
       <c r="BO165" s="6"/>
       <c r="BP165" s="6"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="6"/>
       <c r="BO166" s="6"/>
       <c r="BP166" s="6"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="5" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -8824,7 +8777,7 @@
       <c r="BO167" s="6"/>
       <c r="BP167" s="6"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="4" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -8833,7 +8786,7 @@
       <c r="BO168" s="6"/>
       <c r="BP168" s="6"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="4" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -8842,7 +8795,7 @@
       <c r="BO169" s="6"/>
       <c r="BP169" s="6"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -8854,17 +8807,17 @@
       <c r="BO170" s="6"/>
       <c r="BP170" s="6"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="6"/>
       <c r="BO171" s="6"/>
       <c r="BP171" s="6"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="6"/>
       <c r="BO172" s="6"/>
       <c r="BP172" s="6"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="5" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -8873,7 +8826,7 @@
       <c r="BO173" s="6"/>
       <c r="BP173" s="6"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="4" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -8882,7 +8835,7 @@
       <c r="BO174" s="6"/>
       <c r="BP174" s="6"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -8895,17 +8848,17 @@
       <c r="BO175" s="6"/>
       <c r="BP175" s="6"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="6"/>
       <c r="BO176" s="6"/>
       <c r="BP176" s="6"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="6"/>
       <c r="BO177" s="6"/>
       <c r="BP177" s="6"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="5" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -8914,7 +8867,7 @@
       <c r="BO178" s="6"/>
       <c r="BP178" s="6"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="4" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -8923,39 +8876,39 @@
       <c r="BO179" s="6"/>
       <c r="BP179" s="6"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="27" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="28" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="28" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="28" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="28" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="28" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="25" t="s">
         <v>50</v>
       </c>
@@ -8972,7 +8925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="25" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -8994,7 +8947,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="25" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -9016,7 +8969,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="25" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -9038,7 +8991,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="25" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -9060,7 +9013,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="25" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -9082,7 +9035,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="25" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -9104,7 +9057,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="25" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -9126,7 +9079,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="25" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -9148,7 +9101,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="25" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -9170,7 +9123,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="25" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -9192,7 +9145,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="25" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -9214,7 +9167,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="25" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -9236,7 +9189,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="25" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -9258,31 +9211,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="5" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="4" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="28" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="27" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="25" t="s">
         <v>3</v>
       </c>
@@ -9290,7 +9243,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="25" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -9300,7 +9253,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -9310,13 +9263,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="25" t="s">
         <v>56</v>
       </c>
@@ -9324,7 +9277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="25" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -9334,7 +9287,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -9344,7 +9297,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -9354,7 +9307,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -9364,7 +9317,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -9374,7 +9327,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -9384,7 +9337,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -9394,7 +9347,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -9404,7 +9357,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -9414,7 +9367,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -9424,7 +9377,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -9434,7 +9387,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -9444,25 +9397,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="5" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="4" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="28" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="25" t="s">
         <v>34</v>
       </c>
@@ -9512,7 +9465,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="25" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -9578,7 +9531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -9644,7 +9597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -9710,7 +9663,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -9776,7 +9729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -9842,7 +9795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -9908,7 +9861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -9974,7 +9927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10040,7 +9993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10106,7 +10059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10172,7 +10125,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10238,7 +10191,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10304,7 +10257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10370,7 +10323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10436,7 +10389,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10502,7 +10455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -10568,7 +10521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -10634,7 +10587,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -10700,7 +10653,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -10766,31 +10719,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="5" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="4" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="27" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="25" t="s">
         <v>77</v>
       </c>
@@ -10798,7 +10751,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="25" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -10808,7 +10761,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -10818,17 +10771,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="25" t="s">
         <v>100</v>
       </c>
@@ -10839,7 +10792,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="25" t="s">
         <v>103</v>
       </c>
@@ -10850,7 +10803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="25" t="s">
         <v>105</v>
       </c>
@@ -10861,7 +10814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="25" t="s">
         <v>107</v>
       </c>
@@ -10872,7 +10825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="25" t="s">
         <v>109</v>
       </c>
@@ -10883,7 +10836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="25" t="s">
         <v>111</v>
       </c>
@@ -10894,12 +10847,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="25" t="s">
         <v>100</v>
       </c>
@@ -10910,7 +10863,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="25" t="s">
         <v>114</v>
       </c>
@@ -10921,7 +10874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="25" t="s">
         <v>116</v>
       </c>
@@ -10932,7 +10885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="25" t="s">
         <v>118</v>
       </c>
@@ -10943,7 +10896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="25" t="s">
         <v>120</v>
       </c>
@@ -10954,7 +10907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="25" t="s">
         <v>122</v>
       </c>
@@ -10965,12 +10918,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="25" t="s">
         <v>100</v>
       </c>
@@ -10981,7 +10934,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="25" t="s">
         <v>125</v>
       </c>
@@ -10992,7 +10945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="25" t="s">
         <v>127</v>
       </c>
@@ -11003,7 +10956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="25" t="s">
         <v>129</v>
       </c>
@@ -11014,7 +10967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="25" t="s">
         <v>131</v>
       </c>
@@ -11025,7 +10978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="25" t="s">
         <v>133</v>
       </c>
@@ -11036,12 +10989,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="25" t="s">
         <v>100</v>
       </c>
@@ -11052,7 +11005,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="25" t="s">
         <v>136</v>
       </c>
@@ -11063,7 +11016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="25" t="s">
         <v>138</v>
       </c>
@@ -11074,7 +11027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="25" t="s">
         <v>140</v>
       </c>
@@ -11085,7 +11038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="25" t="s">
         <v>142</v>
       </c>
@@ -11096,7 +11049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="25" t="s">
         <v>144</v>
       </c>
